--- a/BRVM_Portefeuille_Tiaho_09062026.xlsx
+++ b/BRVM_Portefeuille_Tiaho_09062026.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SOGC</t>
+          <t>SOGB</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>SIVC</t>
+          <t>LACI</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>SDSC</t>
+          <t>SDCC</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>BOA CI</t>
+          <t>BOA Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>CBIBF</t>
+          <t>CBBF</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E31" s="44" t="inlineStr">
         <is>
-          <t>Gain &gt;80% (ETIT, CBIBF, NSBC) — envisager une prise de bénéfices partielle</t>
+          <t>Gain &gt;80% (ETIT, CBBF, NSBC) — envisager une prise de bénéfices partielle</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>CBIBF</t>
+          <t>CBBF</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>SDSC</t>
+          <t>SDCC</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>BOA CI</t>
+          <t>BOA Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D13" s="62" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>SOGC</t>
+          <t>SOGB</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>SIVC</t>
+          <t>LACI</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">

--- a/BRVM_Portefeuille_Tiaho_09062026.xlsx
+++ b/BRVM_Portefeuille_Tiaho_09062026.xlsx
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>LACI</t>
+          <t>SIVC</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Air Liquide CI</t>
+          <t>Erium CI (ex-Air Liquide)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>LACI</t>
+          <t>SIVC</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Air Liquide CI</t>
+          <t>Erium CI (ex-Air Liquide)</t>
         </is>
       </c>
       <c r="D18" s="64" t="inlineStr">

--- a/BRVM_Portefeuille_Tiaho_09062026.xlsx
+++ b/BRVM_Portefeuille_Tiaho_09062026.xlsx
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>SDCC</t>
+          <t>SDSC</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>Bolloré Transport CI</t>
+          <t>AGL CI (ex-Bolloré)</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>SDCC</t>
+          <t>SDSC</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Bolloré Transport CI</t>
+          <t>AGL CI (ex-Bolloré)</t>
         </is>
       </c>
       <c r="D11" s="62" t="inlineStr">

--- a/BRVM_Portefeuille_Tiaho_09062026.xlsx
+++ b/BRVM_Portefeuille_Tiaho_09062026.xlsx
@@ -2172,7 +2172,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>4890</v>
+        <v>4834</v>
       </c>
       <c r="G19" s="24">
         <f>E19*F19</f>
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="E23" s="65" t="n">
-        <v>-0.05316973415132924</v>
+        <v>-0.04220107571369466</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>-7800</v>
+        <v>-6120</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>4890</v>
+        <v>4834</v>
       </c>
       <c r="H23" s="55" t="n">
         <v>4630</v>
@@ -3711,14 +3711,14 @@
     <row r="25">
       <c r="A25" s="69" t="inlineStr">
         <is>
-          <t>TOTAL PORTEFEUILLE — Coût : 7,026,271 F  ·  Valeur : 9,316,395 F</t>
+          <t>TOTAL PORTEFEUILLE — Coût : 7,024,591 F  ·  Valeur : 9,316,395 F</t>
         </is>
       </c>
       <c r="E25" s="70" t="n">
-        <v>0.3259373286342073</v>
+        <v>0.3262544395823188</v>
       </c>
       <c r="F25" s="71" t="n">
-        <v>2290124</v>
+        <v>2291804</v>
       </c>
     </row>
   </sheetData>
